--- a/technology_surveys/029_loop_selection_survey--technology_surveys.xlsx
+++ b/technology_surveys/029_loop_selection_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please answer the following questions to help us understand your experience with loops.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,7 +552,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>What kind of projects do you have experience with?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,24 +565,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ease_of_use</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ease_of_use</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>On a scale of 1-5</t>
-        </is>
-      </c>
+          <t>How often do you use loops in your work?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,17 +588,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>loop_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>Which type of loops do you prefer?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>team_involvement</t>
+          <t>ease_of_use</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>team_involvement</t>
+          <t>How easy is it to use loops in your work?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>What kind of resources do you usually use to find help with loops?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>projects_class</t>
+          <t>team_involvement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>projects_class</t>
+          <t>How often do you involve your team in loop-related tasks?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>loop_selection</t>
+          <t>projects_class</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>loop_selection</t>
+          <t>Which type of projects do you usually work on that involve loops?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +703,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>loop_type</t>
+          <t>loop_involvement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>loop_type</t>
+          <t>How involved do you get with your team members when working with loops?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +726,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>difficulties</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>What kind of difficulties do you face when using loops?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>loop_involvement</t>
+          <t>help</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>loop_involvement</t>
+          <t>Which resources do you usually get help from when working with loops?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +772,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ease_of_use</t>
+          <t>preferences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ease_of_use</t>
+          <t>Which kind of loops do you usually prefer?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +795,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>loop_selection</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>Which kind of loops do you usually select?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -818,17 +818,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>team_involvement</t>
+          <t>projects_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>team_involvement</t>
+          <t>Which kind of projects do you usually work on?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>projects_class</t>
+          <t>frequency_loop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>projects_class</t>
+          <t>How often do you use loops in your daily tasks?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +864,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>loop_involvement</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>loop_involvement</t>
+          <t>How involved do you get with your team when working with loops?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +887,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>help_from_team</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>Which kind of help do you usually get from your team when working with loops?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -910,182 +910,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>loop_type</t>
+          <t>projects_in_progress</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>loop_type</t>
+          <t>Which kind of projects do you usually work on that involve loops?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>loop_selection</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>loop_selection</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>projects_class</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>projects_class</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,10 +941,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1135,12 +974,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>projects_i'm_involved_in</t>
+          <t>open-ended_text_input</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Projects I'm involved in</t>
+          <t>Open-ended text input</t>
         </is>
       </c>
     </row>
@@ -1152,12 +991,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>projects_that_are_similar_to_my_job</t>
+          <t>projects_with_loops</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Projects that are similar to my job</t>
+          <t>Projects with loops</t>
         </is>
       </c>
     </row>
@@ -1169,410 +1008,410 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>projects_in_my_industry</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Projects in my industry</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>difficulty_understanding_the_loop</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Difficulty understanding the loop</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>difficulty_using_the_loop_in_my_work</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Difficulty using the loop in my work</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>difficulty_finding_resources_to_help_me_with_the_loop</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Difficulty finding resources to help me with the loop</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>loop_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_involvement_choices</t>
+          <t>loop_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>involving_my_team</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Involving my team</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_involvement_choices</t>
+          <t>loop_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>involving_my_team_members_directly</t>
+          <t>s-closed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Involving my team members directly</t>
+          <t>S-Closed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>team_involvement_choices</t>
+          <t>loop_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>involving_my_team_manager</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Involving my team manager</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>team_involvement_choices</t>
+          <t>ease_of_use_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>ease_of_use_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>ease_of_use_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Hard</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>ease_of_use_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>resources_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>documentation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Documentation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>resources_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Team members</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>resources_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>resources_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>team_involvement_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>on_hold</t>
+          <t>involving_my_team</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>On hold</t>
+          <t>Involving my team</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>team_involvement_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>involving_my_team_members_directly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Involving my team members directly</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>loop_selection_choices</t>
+          <t>team_involvement_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>loop_selection_choices</t>
+          <t>team_involvement_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>loop_type_choices</t>
+          <t>projects_class_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>projects_i'm_currently_working_on</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Projects I'm currently working on</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>loop_type_choices</t>
+          <t>projects_class_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>projects_with_loops</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Projects with loops</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>loop_type_choices</t>
+          <t>projects_class_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>s-closed</t>
+          <t>projects_without_loops</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S-closed</t>
+          <t>Projects without loops</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>loop_type_choices</t>
+          <t>projects_class_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1589,34 +1428,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>loop_involvement_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>projects_i'm_currently_working_on</t>
+          <t>involving_my_team_members</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Projects I'm currently working on</t>
+          <t>Involving my team members</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>loop_involvement_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>involving_my_team_members_prophets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Involving my team members prophets</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1467,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>involving_my_self</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Involving my self</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1484,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>involving_my_team_members</t>
+          <t>involving_my_team_manager</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Involving my team members</t>
+          <t>Involving my team manager</t>
         </is>
       </c>
     </row>
@@ -1662,274 +1501,274 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>involving_my_team_members_prophets</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Involving my team members prophets</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>loop_involvement_choices</t>
+          <t>difficulties_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>difficulty_understanding_the_loop</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Difficulty understanding the loop</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ease_of_use_choices</t>
+          <t>difficulties_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>difficulty_using_the_loop_in_my_work</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Difficulty using the loop in my work</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ease_of_use_choices</t>
+          <t>difficulties_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ease_of_use_choices</t>
+          <t>difficulties_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>difficulty_finding_resources_to_help_me_with_the_loop</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Difficulty finding resources to help me with the loop</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>help_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>documentation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Documentation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>help_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Team members</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>team_involvement_choices</t>
+          <t>help_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>involving_my_team</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Involving my team</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>team_involvement_choices</t>
+          <t>help_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>projects_in_progress</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Projects in progress</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>loop_involvement_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>involving_my_team</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Involving my team</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>loop_involvement_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>involving_my_team_manager</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Involving my team manager</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>loop_involvement_choices</t>
+          <t>loop_selection_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>involving_my_team</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Involving my team</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>loop_selection_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>involving_my_team_members</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Involving my team members</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>loop_selection_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>involving_my_team_members_prophets</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Involving my team members prophets</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>loop_type_choices</t>
+          <t>loop_selection_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1946,41 +1785,41 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>loop_type_choices</t>
+          <t>projects_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>projects_i'm_currently_working_on</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Projects I'm currently working on</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>projects_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>projects_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1997,219 +1836,287 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>frequency_loop_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>involving_my_team_members_directly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Involving my team members directly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>frequency_loop_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>involving_my_team_manager</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Involving my team manager</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>frequency_loop_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>loop_selection_choices</t>
+          <t>frequency_loop_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>loop_selection_choices</t>
+          <t>team_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>involving_my_team</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Involving my team</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>team_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>involving_my_team_members</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Involving my team members</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>team_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>team_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>projects_i've_worked_on_in_the_past</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Projects I've worked on in the past</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>projects_class_choices</t>
+          <t>help_from_team_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>involving_my_team</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Involving my team</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>help_from_team_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>involving_my_team_members</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Involving my team members</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>help_from_team_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>involving_my_team_members_prophets</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Involving my team members prophets</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>help_from_team_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>projects_i've_worked_on_in_the_past</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Projects I've worked on in the past</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>projects_choices</t>
+          <t>help_from_team_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>projects_in_progress_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>projects_with_loops</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Projects with loops</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>projects_in_progress_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>projects_in_progress</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Projects in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>projects_in_progress_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>projects_without_loops</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Projects without loops</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>projects_in_progress_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>none_of_the_above</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>None of the above</t>
         </is>
